--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2557,7 +2557,7 @@
         <v>125891603</v>
       </c>
       <c r="B18" t="n">
-        <v>102568</v>
+        <v>102570</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2557,7 +2557,7 @@
         <v>125891603</v>
       </c>
       <c r="B18" t="n">
-        <v>102570</v>
+        <v>102572</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2557,7 +2557,7 @@
         <v>125891603</v>
       </c>
       <c r="B18" t="n">
-        <v>102572</v>
+        <v>102574</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2557,7 +2557,7 @@
         <v>125891603</v>
       </c>
       <c r="B18" t="n">
-        <v>102574</v>
+        <v>102578</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2557,7 +2557,7 @@
         <v>125891603</v>
       </c>
       <c r="B18" t="n">
-        <v>102578</v>
+        <v>102581</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2557,7 +2557,7 @@
         <v>125891603</v>
       </c>
       <c r="B18" t="n">
-        <v>102581</v>
+        <v>102590</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2664,6 +2664,131 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128715460</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96074</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>210</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Enköping, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>620096</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6611748</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vårfrukyrka</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka fjolårskapslar sitter kvar. Ett tiotal korta årsskaft med unga sporkapslar. Nödtorftigt parerad vid nylig utförd avverkningen för diskgolfhål, precis i kanten av avverkad yta.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>128715460</v>
       </c>
       <c r="B19" t="n">
-        <v>96074</v>
+        <v>96078</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>128715460</v>
       </c>
       <c r="B19" t="n">
-        <v>96078</v>
+        <v>96085</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>128715460</v>
       </c>
       <c r="B19" t="n">
-        <v>96093</v>
+        <v>96098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>128715460</v>
       </c>
       <c r="B19" t="n">
-        <v>96098</v>
+        <v>96101</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>128715460</v>
       </c>
       <c r="B19" t="n">
-        <v>96101</v>
+        <v>96111</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>128715460</v>
       </c>
       <c r="B19" t="n">
-        <v>96111</v>
+        <v>96118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>128715460</v>
       </c>
       <c r="B19" t="n">
-        <v>96118</v>
+        <v>96120</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>128715460</v>
       </c>
       <c r="B19" t="n">
-        <v>96120</v>
+        <v>96146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>128715460</v>
       </c>
       <c r="B19" t="n">
-        <v>96146</v>
+        <v>96147</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>128715460</v>
       </c>
       <c r="B19" t="n">
-        <v>96147</v>
+        <v>96148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>128715460</v>
       </c>
       <c r="B19" t="n">
-        <v>96148</v>
+        <v>96152</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2669,7 +2669,7 @@
         <v>128715460</v>
       </c>
       <c r="B19" t="n">
-        <v>96152</v>
+        <v>96154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112269128</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,6 +927,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120738973</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120739248</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1149,6 +1169,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121148350</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125071836</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1377,6 +1407,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128686879</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1502,6 +1537,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128715460</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1626,6 +1666,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112262930</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1750,6 +1795,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112262737</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1874,6 +1924,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112270057</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1981,6 +2036,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121461172</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2102,6 +2162,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121461626</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2199,6 +2264,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123283860</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2323,6 +2393,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96386711</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2440,6 +2515,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112260758</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2564,6 +2644,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112260815</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2671,6 +2756,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120739480</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2778,6 +2868,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740395</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2885,6 +2980,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120762521</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2993,6 +3093,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112269301</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3109,6 +3214,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112271270</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3225,6 +3335,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120741020</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3341,6 +3456,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120741100</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3443,6 +3563,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95461684</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3550,6 +3675,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127502927</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3667,6 +3797,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112260428</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3789,6 +3924,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112263050</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3902,6 +4042,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96386566</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4003,6 +4148,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96390160</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4119,6 +4269,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96400114</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4240,6 +4395,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120739622</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4356,6 +4516,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120743373</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4463,6 +4628,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120743415</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4587,6 +4757,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112266904</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4696,6 +4871,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96390113</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4813,6 +4993,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112261300</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4930,6 +5115,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112268652</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5038,6 +5228,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112269331</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5155,6 +5350,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112270608</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5277,6 +5477,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112271243</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5393,6 +5598,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120742853</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5509,6 +5719,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120746156</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5625,6 +5840,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120762634</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5741,6 +5961,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120744438</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5863,6 +6088,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112261767</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5973,6 +6203,11 @@
           <t>Enköpings kommun - Mångbruksplan</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113910235</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6085,6 +6320,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121462885</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6191,6 +6431,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122179220</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6310,6 +6555,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133681471</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6420,6 +6670,11 @@
           <t>Enköpings kommun - Mångbruksplan</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113910192</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6530,6 +6785,11 @@
           <t>Enköpings kommun - Mångbruksplan</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113910193</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6652,6 +6912,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112270237</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6762,6 +7027,11 @@
           <t>Enköpings kommun - Mångbruksplan</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113910190</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6872,6 +7142,11 @@
           <t>Enköpings kommun - Mångbruksplan</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113910195</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6979,6 +7254,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122394341</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7091,6 +7371,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120762763</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7208,6 +7493,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357718</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7310,6 +7600,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123284268</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7417,6 +7712,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125072502</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7534,6 +7834,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112260078</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7647,6 +7952,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112267966</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7759,6 +8069,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120740357</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7871,6 +8186,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121082771</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7978,6 +8298,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121082939</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8090,6 +8415,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143984</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8202,6 +8532,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121144661</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8328,6 +8663,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122354895</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8440,8 +8780,83 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125891603</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ69"/>
+  <dimension ref="A1:AZ71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2272,59 +2272,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96386711</v>
+        <v>136125908</v>
       </c>
       <c r="B15" t="n">
-        <v>92564</v>
+        <v>92497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Enköping, Upl</t>
+          <t>Gånsta öst, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620010</v>
+        <v>620053</v>
       </c>
       <c r="R15" t="n">
-        <v>6611472</v>
+        <v>6611311</v>
       </c>
       <c r="S15" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2348,27 +2346,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:42</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ett tiotal fruktkroppar på granlåga, nära diket. Fin sumpskog trots diket.</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2377,7 +2370,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2395,13 +2387,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96386711</t>
+          <t>https://artportalen.se/Sighting/136125908</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112260758</v>
+        <v>96386711</v>
       </c>
       <c r="B16" t="n">
         <v>92564</v>
@@ -2431,7 +2423,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2440,19 +2432,20 @@
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gånsta öst, mot Österleden, Upl</t>
+          <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620354</v>
+        <v>620010</v>
       </c>
       <c r="R16" t="n">
-        <v>6611551</v>
+        <v>6611472</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2476,22 +2469,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ett tiotal fruktkroppar på granlåga, nära diket. Fin sumpskog trots diket.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2500,6 +2498,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2517,13 +2516,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112260758</t>
+          <t>https://artportalen.se/Sighting/96386711</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112260815</v>
+        <v>112260758</v>
       </c>
       <c r="B17" t="n">
         <v>92564</v>
@@ -2553,7 +2552,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2562,17 +2561,16 @@
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gånsta O, Upl</t>
+          <t>Gånsta öst, mot Österleden, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620338</v>
+        <v>620354</v>
       </c>
       <c r="R17" t="n">
-        <v>6611532</v>
+        <v>6611551</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2604,7 +2602,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2614,7 +2612,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2623,39 +2621,33 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg, Anders Lindholm</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112260815</t>
+          <t>https://artportalen.se/Sighting/112260758</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120739480</v>
+        <v>112260815</v>
       </c>
       <c r="B18" t="n">
-        <v>96458</v>
+        <v>92564</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2663,37 +2655,48 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2818</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Enköping, Enköping, Upl</t>
+          <t>Gånsta O, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>619780</v>
+        <v>620338</v>
       </c>
       <c r="R18" t="n">
-        <v>6611786</v>
+        <v>6611532</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2717,22 +2720,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2741,30 +2744,36 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Gabriel Tjernberg, Anders Lindholm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120739480</t>
+          <t>https://artportalen.se/Sighting/112260815</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120740395</v>
+        <v>120739480</v>
       </c>
       <c r="B19" t="n">
         <v>96458</v>
@@ -2799,10 +2808,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>619805</v>
+        <v>619780</v>
       </c>
       <c r="R19" t="n">
-        <v>6611765</v>
+        <v>6611786</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2834,7 +2843,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2844,7 +2853,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2870,13 +2879,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120740395</t>
+          <t>https://artportalen.se/Sighting/120739480</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120762521</v>
+        <v>120740395</v>
       </c>
       <c r="B20" t="n">
         <v>96458</v>
@@ -2907,17 +2916,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Enköping, Upl</t>
+          <t>Enköping, Enköping, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>619966</v>
+        <v>619805</v>
       </c>
       <c r="R20" t="n">
-        <v>6611659</v>
+        <v>6611765</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2941,22 +2950,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2982,16 +2991,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120762521</t>
+          <t>https://artportalen.se/Sighting/120740395</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112269301</v>
+        <v>120762521</v>
       </c>
       <c r="B21" t="n">
-        <v>91680</v>
+        <v>96458</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2999,35 +3008,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3215</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gånsta öst, Upl</t>
+          <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620263</v>
+        <v>619966</v>
       </c>
       <c r="R21" t="n">
-        <v>6611434</v>
+        <v>6611659</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3054,22 +3062,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3095,13 +3103,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112269301</t>
+          <t>https://artportalen.se/Sighting/120762521</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112271270</v>
+        <v>112269301</v>
       </c>
       <c r="B22" t="n">
         <v>91680</v>
@@ -3130,19 +3138,17 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gånsta öst, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>619987</v>
+        <v>620263</v>
       </c>
       <c r="R22" t="n">
-        <v>6611603</v>
+        <v>6611434</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3174,7 +3180,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3184,12 +3190,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt i granskog med intakt fukt- sumpskogshydrologi. Flera förekomster, flera mycel inom nga tiotal meter.</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3198,7 +3199,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3216,16 +3216,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112271270</t>
+          <t>https://artportalen.se/Sighting/112269301</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120741020</v>
+        <v>112271270</v>
       </c>
       <c r="B23" t="n">
-        <v>91330</v>
+        <v>91680</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3233,46 +3233,40 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4189</v>
+        <v>3215</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Enköping, Upl</t>
+          <t>Gånsta öst, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>619857</v>
+        <v>619987</v>
       </c>
       <c r="R23" t="n">
-        <v>6611730</v>
+        <v>6611603</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3296,22 +3290,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt i granskog med intakt fukt- sumpskogshydrologi. Flera förekomster, flera mycel inom nga tiotal meter.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3320,30 +3319,31 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120741020</t>
+          <t>https://artportalen.se/Sighting/112271270</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120741100</v>
+        <v>120741020</v>
       </c>
       <c r="B24" t="n">
         <v>91330</v>
@@ -3383,17 +3383,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Enköping, Enköping, Upl</t>
+          <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>619847</v>
+        <v>619857</v>
       </c>
       <c r="R24" t="n">
         <v>6611730</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3447,49 +3447,49 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120741100</t>
+          <t>https://artportalen.se/Sighting/120741020</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>95461684</v>
+        <v>120741100</v>
       </c>
       <c r="B25" t="n">
-        <v>93189</v>
+        <v>91330</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>4189</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Pers., nom.sanct</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3497,20 +3497,24 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Östra Länken, Enköping, Upl</t>
+          <t>Enköping, Enköping, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620141</v>
+        <v>619847</v>
       </c>
       <c r="R25" t="n">
-        <v>6611685</v>
+        <v>6611730</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3534,12 +3538,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-08-13</t>
+          <t>2024-10-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3554,27 +3568,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Karin Tempelman</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Karin Tempelman</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95461684</t>
+          <t>https://artportalen.se/Sighting/120741100</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127502927</v>
+        <v>95461684</v>
       </c>
       <c r="B26" t="n">
-        <v>93197</v>
+        <v>93189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3582,37 +3596,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Enköping, Upl</t>
+          <t>Östra Länken, Enköping, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620333</v>
+        <v>620141</v>
       </c>
       <c r="R26" t="n">
-        <v>6611512</v>
+        <v>6611685</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3636,22 +3655,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2021-08-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3666,27 +3675,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Karin Tempelman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Karin Tempelman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127502927</t>
+          <t>https://artportalen.se/Sighting/95461684</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112260428</v>
+        <v>127502927</v>
       </c>
       <c r="B27" t="n">
-        <v>93209</v>
+        <v>93197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3694,47 +3703,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gånsta öst, Upl</t>
+          <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620344</v>
+        <v>620333</v>
       </c>
       <c r="R27" t="n">
-        <v>6611529</v>
+        <v>6611512</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3758,22 +3757,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3788,24 +3787,24 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Lindholm, Gabriel Tjernberg</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112260428</t>
+          <t>https://artportalen.se/Sighting/127502927</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112263050</v>
+        <v>112260428</v>
       </c>
       <c r="B28" t="n">
         <v>93209</v>
@@ -3835,7 +3834,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3846,14 +3845,14 @@
       <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gånsta O, Upl</t>
+          <t>Gånsta öst, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620261</v>
+        <v>620344</v>
       </c>
       <c r="R28" t="n">
-        <v>6611674</v>
+        <v>6611529</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3885,7 +3884,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3895,7 +3894,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3906,75 +3905,79 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg, Anders Lindholm</t>
+          <t>Anders Lindholm, Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112263050</t>
+          <t>https://artportalen.se/Sighting/112260428</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96386566</v>
+        <v>112263050</v>
       </c>
       <c r="B29" t="n">
-        <v>92869</v>
+        <v>93209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Enköping, Upl</t>
+          <t>Gånsta O, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620015</v>
+        <v>620261</v>
       </c>
       <c r="R29" t="n">
-        <v>6611603</v>
+        <v>6611674</v>
       </c>
       <c r="S29" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3998,27 +4001,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:32</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4029,28 +4027,33 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Gabriel Tjernberg, Anders Lindholm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96386566</t>
+          <t>https://artportalen.se/Sighting/112263050</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96390160</v>
+        <v>96386566</v>
       </c>
       <c r="B30" t="n">
         <v>92869</v>
@@ -4079,22 +4082,20 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620232</v>
+        <v>620015</v>
       </c>
       <c r="R30" t="n">
-        <v>6611425</v>
+        <v>6611603</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4121,18 +4122,32 @@
           <t>2021-09-30</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2021-09-30</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4150,13 +4165,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96390160</t>
+          <t>https://artportalen.se/Sighting/96386566</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>96400114</v>
+        <v>96390160</v>
       </c>
       <c r="B31" t="n">
         <v>92869</v>
@@ -4194,13 +4209,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620018</v>
+        <v>620232</v>
       </c>
       <c r="R31" t="n">
-        <v>6611608</v>
+        <v>6611425</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4227,24 +4242,9 @@
           <t>2021-09-30</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2021-09-30</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>I västsluttningen.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4271,13 +4271,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96400114</t>
+          <t>https://artportalen.se/Sighting/96390160</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120739622</v>
+        <v>96400114</v>
       </c>
       <c r="B32" t="n">
         <v>92869</v>
@@ -4305,29 +4305,23 @@
           <t>(Scop.) Fr.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Enköping, Enköping, Upl</t>
+          <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>619767</v>
+        <v>620018</v>
       </c>
       <c r="R32" t="n">
-        <v>6611810</v>
+        <v>6611608</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4351,27 +4345,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>3 fruktkroppar</t>
+          <t>I västsluttningen.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4380,6 +4374,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4397,13 +4392,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120739622</t>
+          <t>https://artportalen.se/Sighting/96400114</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120743373</v>
+        <v>120739622</v>
       </c>
       <c r="B33" t="n">
         <v>92869</v>
@@ -4438,7 +4433,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4447,10 +4442,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>619945</v>
+        <v>619767</v>
       </c>
       <c r="R33" t="n">
-        <v>6611689</v>
+        <v>6611810</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4482,7 +4477,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4492,7 +4487,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>3 fruktkroppar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4518,13 +4518,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120743373</t>
+          <t>https://artportalen.se/Sighting/120739622</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120743415</v>
+        <v>120743373</v>
       </c>
       <c r="B34" t="n">
         <v>92869</v>
@@ -4552,20 +4552,29 @@
           <t>(Scop.) Fr.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Enköping, Upl</t>
+          <t>Enköping, Enköping, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>619957</v>
+        <v>619945</v>
       </c>
       <c r="R34" t="n">
-        <v>6611691</v>
+        <v>6611689</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4594,7 +4603,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4604,7 +4613,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4619,27 +4628,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120743415</t>
+          <t>https://artportalen.se/Sighting/120743373</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112266904</v>
+        <v>120743415</v>
       </c>
       <c r="B35" t="n">
-        <v>92348</v>
+        <v>92869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4647,48 +4656,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5420</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gånsta öst, Upl</t>
+          <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620335</v>
+        <v>619957</v>
       </c>
       <c r="R35" t="n">
-        <v>6611490</v>
+        <v>6611691</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4712,27 +4710,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Mycket stora fruktkroppar kring en död stående tall.</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4741,80 +4734,79 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Lindholm, Gabriel Tjernberg</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112266904</t>
+          <t>https://artportalen.se/Sighting/120743415</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>96390113</v>
+        <v>112266904</v>
       </c>
       <c r="B36" t="n">
-        <v>93233</v>
+        <v>92348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5964</v>
+        <v>5420</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Enköping, Upl</t>
+          <t>Gånsta öst, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620286</v>
+        <v>620335</v>
       </c>
       <c r="R36" t="n">
-        <v>6611403</v>
+        <v>6611490</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4841,12 +4833,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2021-09-30</t>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Mycket stora fruktkroppar kring en död stående tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4867,19 +4874,19 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Anders Lindholm, Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96390113</t>
+          <t>https://artportalen.se/Sighting/112266904</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112261300</v>
+        <v>96390113</v>
       </c>
       <c r="B37" t="n">
         <v>93233</v>
@@ -4914,20 +4921,21 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gånsta öst, Upl</t>
+          <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620354</v>
+        <v>620286</v>
       </c>
       <c r="R37" t="n">
-        <v>6611602</v>
+        <v>6611403</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4954,22 +4962,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>2021-09-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4978,6 +4976,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4995,13 +4994,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112261300</t>
+          <t>https://artportalen.se/Sighting/96390113</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112268652</v>
+        <v>112261300</v>
       </c>
       <c r="B38" t="n">
         <v>93233</v>
@@ -5036,7 +5035,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -5046,10 +5045,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620298</v>
+        <v>620354</v>
       </c>
       <c r="R38" t="n">
-        <v>6611435</v>
+        <v>6611602</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5081,7 +5080,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5091,7 +5090,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5117,13 +5116,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112268652</t>
+          <t>https://artportalen.se/Sighting/112261300</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112269331</v>
+        <v>112268652</v>
       </c>
       <c r="B39" t="n">
         <v>93233</v>
@@ -5151,7 +5150,16 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5159,10 +5167,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620266</v>
+        <v>620298</v>
       </c>
       <c r="R39" t="n">
-        <v>6611482</v>
+        <v>6611435</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5194,7 +5202,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5204,7 +5212,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5230,13 +5238,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112269331</t>
+          <t>https://artportalen.se/Sighting/112268652</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112270608</v>
+        <v>112269331</v>
       </c>
       <c r="B40" t="n">
         <v>93233</v>
@@ -5264,16 +5272,7 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5281,10 +5280,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620020</v>
+        <v>620266</v>
       </c>
       <c r="R40" t="n">
-        <v>6611431</v>
+        <v>6611482</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5316,7 +5315,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5326,7 +5325,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5352,13 +5351,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112270608</t>
+          <t>https://artportalen.se/Sighting/112269331</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112271243</v>
+        <v>112270608</v>
       </c>
       <c r="B41" t="n">
         <v>93233</v>
@@ -5388,25 +5387,25 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gånsta O, Upl</t>
+          <t>Gånsta öst, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620014</v>
+        <v>620020</v>
       </c>
       <c r="R41" t="n">
-        <v>6611604</v>
+        <v>6611431</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5438,7 +5437,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5448,7 +5447,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5459,33 +5458,28 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg, Anders Lindholm</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112271243</t>
+          <t>https://artportalen.se/Sighting/112270608</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120742853</v>
+        <v>112271243</v>
       </c>
       <c r="B42" t="n">
         <v>93233</v>
@@ -5515,7 +5509,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5523,19 +5517,20 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Enköping, Upl</t>
+          <t>Gånsta O, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>619875</v>
+        <v>620014</v>
       </c>
       <c r="R42" t="n">
-        <v>6611629</v>
+        <v>6611604</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5559,22 +5554,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5585,28 +5580,33 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Gabriel Tjernberg, Anders Lindholm</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120742853</t>
+          <t>https://artportalen.se/Sighting/112271243</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120746156</v>
+        <v>120742853</v>
       </c>
       <c r="B43" t="n">
         <v>93233</v>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5650,13 +5650,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620270</v>
+        <v>619875</v>
       </c>
       <c r="R43" t="n">
-        <v>6611479</v>
+        <v>6611629</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5710,24 +5710,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120746156</t>
+          <t>https://artportalen.se/Sighting/120742853</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120762634</v>
+        <v>120746156</v>
       </c>
       <c r="B44" t="n">
         <v>93233</v>
@@ -5757,7 +5757,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5771,13 +5771,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>619976</v>
+        <v>620270</v>
       </c>
       <c r="R44" t="n">
-        <v>6611604</v>
+        <v>6611479</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5801,22 +5801,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5831,27 +5831,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120762634</t>
+          <t>https://artportalen.se/Sighting/120746156</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120744438</v>
+        <v>120762634</v>
       </c>
       <c r="B45" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5859,26 +5859,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5892,13 +5892,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620180</v>
+        <v>619976</v>
       </c>
       <c r="R45" t="n">
-        <v>6611651</v>
+        <v>6611604</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5952,49 +5952,49 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120744438</t>
+          <t>https://artportalen.se/Sighting/120762634</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112261767</v>
+        <v>120744438</v>
       </c>
       <c r="B46" t="n">
-        <v>92567</v>
+        <v>93235</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6007,17 +6007,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gånsta O, Upl</t>
+          <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620313</v>
+        <v>620180</v>
       </c>
       <c r="R46" t="n">
-        <v>6611646</v>
+        <v>6611651</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6044,22 +6043,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6070,33 +6069,28 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg, Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112261767</t>
+          <t>https://artportalen.se/Sighting/120744438</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113910235</v>
+        <v>112261767</v>
       </c>
       <c r="B47" t="n">
         <v>92567</v>
@@ -6134,19 +6128,20 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ängslyckan, Upl</t>
+          <t>Gånsta O, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620322</v>
+        <v>620313</v>
       </c>
       <c r="R47" t="n">
-        <v>6611641</v>
+        <v>6611646</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6170,12 +6165,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6186,35 +6191,36 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Adam Ekholm</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Enköpings kommun - Mångbruksplan</t>
-        </is>
-      </c>
+          <t>Gabriel Tjernberg, Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113910235</t>
+          <t>https://artportalen.se/Sighting/112261767</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121462885</v>
+        <v>113910235</v>
       </c>
       <c r="B48" t="n">
-        <v>57950</v>
+        <v>92567</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6222,37 +6228,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gånsta öst, Upl</t>
+          <t>Ängslyckan, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620365</v>
+        <v>620322</v>
       </c>
       <c r="R48" t="n">
-        <v>6611460</v>
+        <v>6611641</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6276,27 +6291,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Flygande från norr, landade tillfälligt i tall.</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6311,24 +6311,28 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Adam Ekholm</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Enköpings kommun - Mångbruksplan</t>
+        </is>
+      </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121462885</t>
+          <t>https://artportalen.se/Sighting/113910235</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122179220</v>
+        <v>121462885</v>
       </c>
       <c r="B49" t="n">
         <v>57950</v>
@@ -6356,29 +6360,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Enköping, Enköping, Upl</t>
+          <t>Gånsta öst, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>619893</v>
+        <v>620365</v>
       </c>
       <c r="R49" t="n">
-        <v>6611591</v>
+        <v>6611460</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6402,12 +6397,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Flygande från norr, landade tillfälligt i tall.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6422,27 +6432,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122179220</t>
+          <t>https://artportalen.se/Sighting/121462885</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133681471</v>
+        <v>122179220</v>
       </c>
       <c r="B50" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6469,30 +6479,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>O om Sandsoppsgatan, Gånsta discgolfbana, Enköping, Upl</t>
+          <t>Enköping, Enköping, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>619882</v>
+        <v>619893</v>
       </c>
       <c r="R50" t="n">
-        <v>6611677</v>
+        <v>6611591</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6516,22 +6523,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6546,27 +6543,27 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ingrid Åkerberg</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ingrid Åkerberg</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133681471</t>
+          <t>https://artportalen.se/Sighting/122179220</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>113910192</v>
+        <v>133681471</v>
       </c>
       <c r="B51" t="n">
-        <v>5179</v>
+        <v>57972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6574,21 +6571,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6596,24 +6593,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ängslyckan, Upl</t>
+          <t>O om Sandsoppsgatan, Gånsta discgolfbana, Enköping, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620338</v>
+        <v>619882</v>
       </c>
       <c r="R51" t="n">
-        <v>6611455</v>
+        <v>6611677</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6637,12 +6637,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6657,28 +6667,24 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Ingrid Åkerberg</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Adam Ekholm</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Enköpings kommun - Mångbruksplan</t>
-        </is>
-      </c>
+          <t>Ingrid Åkerberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113910192</t>
+          <t>https://artportalen.se/Sighting/133681471</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>113910193</v>
+        <v>113910192</v>
       </c>
       <c r="B52" t="n">
         <v>5179</v>
@@ -6722,13 +6728,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620315</v>
+        <v>620338</v>
       </c>
       <c r="R52" t="n">
-        <v>6611583</v>
+        <v>6611455</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6787,38 +6793,38 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113910193</t>
+          <t>https://artportalen.se/Sighting/113910192</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112270237</v>
+        <v>113910193</v>
       </c>
       <c r="B53" t="n">
-        <v>58114</v>
+        <v>5179</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6826,25 +6832,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gånsta O, Upl</t>
+          <t>Ängslyckan, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620128</v>
+        <v>620315</v>
       </c>
       <c r="R53" t="n">
-        <v>6611373</v>
+        <v>6611583</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6868,22 +6873,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6894,58 +6889,57 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg, Anders Lindholm</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Adam Ekholm</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Enköpings kommun - Mångbruksplan</t>
+        </is>
+      </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112270237</t>
+          <t>https://artportalen.se/Sighting/113910193</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113910190</v>
+        <v>112270237</v>
       </c>
       <c r="B54" t="n">
-        <v>5199</v>
+        <v>58114</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -6953,24 +6947,25 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ängslyckan, Upl</t>
+          <t>Gånsta O, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620084</v>
+        <v>620128</v>
       </c>
       <c r="R54" t="n">
-        <v>6611275</v>
+        <v>6611373</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6994,12 +6989,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7010,57 +7015,58 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Adam Ekholm</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Enköpings kommun - Mångbruksplan</t>
-        </is>
-      </c>
+          <t>Gabriel Tjernberg, Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113910190</t>
+          <t>https://artportalen.se/Sighting/112270237</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113910195</v>
+        <v>136126655</v>
       </c>
       <c r="B55" t="n">
-        <v>5199</v>
+        <v>58143</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -7070,22 +7076,22 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ängslyckan, Upl</t>
+          <t>Gånsta öst, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620318</v>
+        <v>619907</v>
       </c>
       <c r="R55" t="n">
-        <v>6611585</v>
+        <v>6611400</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7109,12 +7115,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7129,28 +7145,24 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Greensway AB</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Adam Ekholm</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Enköpings kommun - Mångbruksplan</t>
-        </is>
-      </c>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113910195</t>
+          <t>https://artportalen.se/Sighting/136126655</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122394341</v>
+        <v>113910190</v>
       </c>
       <c r="B56" t="n">
         <v>5199</v>
@@ -7178,20 +7190,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Enköping, Upl</t>
+          <t>Ängslyckan, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>620227</v>
+        <v>620084</v>
       </c>
       <c r="R56" t="n">
-        <v>6611391</v>
+        <v>6611275</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7215,22 +7236,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7245,44 +7256,48 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Adam Ekholm</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Enköpings kommun - Mångbruksplan</t>
+        </is>
+      </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122394341</t>
+          <t>https://artportalen.se/Sighting/113910190</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120762763</v>
+        <v>113910195</v>
       </c>
       <c r="B57" t="n">
-        <v>56689</v>
+        <v>5199</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>206046</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7290,25 +7305,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Enköping, Upl</t>
+          <t>Ängslyckan, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>619976</v>
+        <v>620318</v>
       </c>
       <c r="R57" t="n">
-        <v>6611604</v>
+        <v>6611585</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7332,22 +7351,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-30</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2023-11-03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7362,44 +7371,48 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Greensway AB</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Adam Ekholm</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Enköpings kommun - Mångbruksplan</t>
+        </is>
+      </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120762763</t>
+          <t>https://artportalen.se/Sighting/113910195</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122357718</v>
+        <v>122394341</v>
       </c>
       <c r="B58" t="n">
-        <v>56689</v>
+        <v>5199</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>206046</v>
+        <v>105930</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7408,24 +7421,19 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>620286</v>
+        <v>620227</v>
       </c>
       <c r="R58" t="n">
-        <v>6611691</v>
+        <v>6611391</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7449,27 +7457,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Spillning från senaste månaderna.</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7484,24 +7487,24 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122357718</t>
+          <t>https://artportalen.se/Sighting/122394341</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123284268</v>
+        <v>120762763</v>
       </c>
       <c r="B59" t="n">
         <v>56689</v>
@@ -7532,7 +7535,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7541,13 +7544,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>620172</v>
+        <v>619976</v>
       </c>
       <c r="R59" t="n">
-        <v>6611357</v>
+        <v>6611604</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7571,12 +7574,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7591,65 +7604,70 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123284268</t>
+          <t>https://artportalen.se/Sighting/120762763</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125072502</v>
+        <v>122357718</v>
       </c>
       <c r="B60" t="n">
-        <v>106244</v>
+        <v>56689</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>206046</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>619921</v>
+        <v>620286</v>
       </c>
       <c r="R60" t="n">
-        <v>6611441</v>
+        <v>6611691</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7673,22 +7691,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Spillning från senaste månaderna.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7703,69 +7726,70 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125072502</t>
+          <t>https://artportalen.se/Sighting/122357718</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112260078</v>
+        <v>123284268</v>
       </c>
       <c r="B61" t="n">
-        <v>101326</v>
+        <v>56689</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>206046</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gånsta öst, mot Österleden, Upl</t>
+          <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>620354</v>
+        <v>620172</v>
       </c>
       <c r="R61" t="n">
-        <v>6611551</v>
+        <v>6611357</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7789,27 +7813,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Inom 4 m2. I hakmossematta. Även smultron. Äldre granskog med flertal lågor.</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7818,34 +7827,33 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112260078</t>
+          <t>https://artportalen.se/Sighting/123284268</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112267966</v>
+        <v>125072502</v>
       </c>
       <c r="B62" t="n">
-        <v>101326</v>
+        <v>106244</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7853,38 +7861,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gånsta O, Upl</t>
+          <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>620279</v>
+        <v>619921</v>
       </c>
       <c r="R62" t="n">
-        <v>6611416</v>
+        <v>6611441</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7908,22 +7915,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7934,33 +7941,28 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg, Anders Lindholm</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112267966</t>
+          <t>https://artportalen.se/Sighting/125072502</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120740357</v>
+        <v>112260078</v>
       </c>
       <c r="B63" t="n">
         <v>101326</v>
@@ -7989,19 +7991,23 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Enköping, Enköping, Upl</t>
+          <t>Gånsta öst, mot Österleden, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>619805</v>
+        <v>620354</v>
       </c>
       <c r="R63" t="n">
-        <v>6611768</v>
+        <v>6611551</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8025,27 +8031,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Mkt rikligt med blåsippsblad inom ca 75 m2.</t>
+          <t>Inom 4 m2. I hakmossematta. Även smultron. Äldre granskog med flertal lågor.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8054,6 +8060,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -8071,13 +8078,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120740357</t>
+          <t>https://artportalen.se/Sighting/112260078</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121082771</v>
+        <v>112267966</v>
       </c>
       <c r="B64" t="n">
         <v>101326</v>
@@ -8106,19 +8113,20 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Enköping, Enköping, Upl</t>
+          <t>Gånsta O, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>619819</v>
+        <v>620279</v>
       </c>
       <c r="R64" t="n">
-        <v>6611754</v>
+        <v>6611416</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8142,27 +8150,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8173,28 +8176,33 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Gabriel Tjernberg, Anders Lindholm</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121082771</t>
+          <t>https://artportalen.se/Sighting/112267966</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121082939</v>
+        <v>120740357</v>
       </c>
       <c r="B65" t="n">
         <v>101326</v>
@@ -8229,13 +8237,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>619798</v>
+        <v>619805</v>
       </c>
       <c r="R65" t="n">
-        <v>6611789</v>
+        <v>6611768</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8259,22 +8267,27 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Mkt rikligt med blåsippsblad inom ca 75 m2.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8300,13 +8313,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121082939</t>
+          <t>https://artportalen.se/Sighting/120740357</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121143984</v>
+        <v>121082771</v>
       </c>
       <c r="B66" t="n">
         <v>101326</v>
@@ -8337,17 +8350,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Enköping, Upl</t>
+          <t>Enköping, Enköping, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>619749</v>
+        <v>619819</v>
       </c>
       <c r="R66" t="n">
-        <v>6611810</v>
+        <v>6611754</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8371,27 +8384,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>10 spridda plantor inom 5 m radie, bland kransmossa.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8417,13 +8430,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121143984</t>
+          <t>https://artportalen.se/Sighting/121082771</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121144661</v>
+        <v>121082939</v>
       </c>
       <c r="B67" t="n">
         <v>101326</v>
@@ -8458,13 +8471,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>619783</v>
+        <v>619798</v>
       </c>
       <c r="R67" t="n">
-        <v>6611784</v>
+        <v>6611789</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8488,27 +8501,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-12</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt i ca 30-årig tallplantering påfrisk mark med kalkinslag.</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8534,13 +8542,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121144661</t>
+          <t>https://artportalen.se/Sighting/121082939</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122354895</v>
+        <v>121143984</v>
       </c>
       <c r="B68" t="n">
         <v>101326</v>
@@ -8568,31 +8576,17 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Enköping, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>620127</v>
+        <v>619749</v>
       </c>
       <c r="R68" t="n">
-        <v>6611759</v>
+        <v>6611810</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8619,27 +8613,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Inom 1 kvadratmeter.</t>
+          <t>10 spridda plantor inom 5 m radie, bland kransmossa.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8665,54 +8659,54 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122354895</t>
+          <t>https://artportalen.se/Sighting/121143984</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125891603</v>
+        <v>121144661</v>
       </c>
       <c r="B69" t="n">
-        <v>103403</v>
+        <v>101326</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>223246</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Enköping, Upl</t>
+          <t>Enköping, Enköping, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>619976</v>
+        <v>619783</v>
       </c>
       <c r="R69" t="n">
-        <v>6611410</v>
+        <v>6611784</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8736,27 +8730,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Frisk</t>
+          <t>Rikligt i ca 30-årig tallplantering påfrisk mark med kalkinslag.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8771,16 +8765,264 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121144661</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>122354895</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Enköping, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>620127</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6611759</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Vårfrukyrka</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Inom 1 kvadratmeter.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122354895</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125891603</v>
+      </c>
+      <c r="B71" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Enköping, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>619976</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6611410</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Vårfrukyrka</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Frisk</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125891603</t>
         </is>
@@ -8856,6 +9098,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2275,7 +2275,7 @@
         <v>136125908</v>
       </c>
       <c r="B15" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2275,7 +2275,7 @@
         <v>136125908</v>
       </c>
       <c r="B15" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>136126655</v>
       </c>
       <c r="B55" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2275,7 +2275,7 @@
         <v>136125908</v>
       </c>
       <c r="B15" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>136126655</v>
       </c>
       <c r="B55" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 30851-2025 artfynd.xlsx
+++ b/artfynd/A 30851-2025 artfynd.xlsx
@@ -2275,7 +2275,7 @@
         <v>136125908</v>
       </c>
       <c r="B15" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>136126655</v>
       </c>
       <c r="B55" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
